--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_20-05-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_20-05-2026.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>£16.58</t>
+          <t>£17.08</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>£16.99</t>
+          <t>Error: HTTPSConnectionPool(host='www.tradeinsulations.co.uk', port=443): Max retries exceeded with url: /product/30mm-celotex-insulation-board-tb4030-2400mm-x-1200mm-x-30mm/ (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.tradeinsulations.co.uk', port=443) at 0x2169ff0bbd0&gt;, 'Connection to www.tradeinsulations.co.uk timed out. (connect timeout=30)'))</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>£20.51</t>
+          <t>£21.13</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>£23.90</t>
+          <t>£24.62</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>£32.23</t>
+          <t>£33.20</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>£34.29</t>
+          <t>£35.32</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>£36.15</t>
+          <t>£37.23</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>£39.31</t>
+          <t>£40.49</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>£44.86</t>
+          <t>£46.21</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>£43.08</t>
+          <t>£44.37</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>£47.73</t>
+          <t>£49.16</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>£53.55</t>
+          <t>£55.16</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>£60.42</t>
+          <t>£62.23</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>£62.58</t>
+          <t>£64.46</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>£1102.63</t>
+          <t>£1135.71</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2015,24 +2015,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.building-supplies-online.co.uk/products/celotex-xr4200-200mm-x-2-4m-x-1-2m-pallet-of-12</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>£1,295.00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>£1800.0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>£1,295.00</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>£1800.0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>£1,295.00</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>£1427.4</t>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>£1487.20</t>
+          <t>£1531.82</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>£39.46</t>
+          <t>£40.64</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>£48.01</t>
+          <t>£49.45</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>£51.44</t>
+          <t>£52.97</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>£61.74</t>
+          <t>£63.59</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>£66.26</t>
+          <t>£68.25</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>£64.20</t>
+          <t>£66.13</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>£61.87</t>
+          <t>£63.73</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>£1905.76</t>
+          <t>£1962.88</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>£2143.36</t>
+          <t>£2207.68</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
